--- a/data/nzd0536/nzd0536.xlsx
+++ b/data/nzd0536/nzd0536.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G500"/>
+  <dimension ref="A1:G503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13936,6 +13936,87 @@
         <v>322.69</v>
       </c>
       <c r="G500" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>330.79</v>
+      </c>
+      <c r="C501" t="n">
+        <v>326.4</v>
+      </c>
+      <c r="D501" t="n">
+        <v>317.7</v>
+      </c>
+      <c r="E501" t="n">
+        <v>317.37</v>
+      </c>
+      <c r="F501" t="n">
+        <v>324.11</v>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>330.59</v>
+      </c>
+      <c r="C502" t="n">
+        <v>326.79</v>
+      </c>
+      <c r="D502" t="n">
+        <v>317.74</v>
+      </c>
+      <c r="E502" t="n">
+        <v>318.03</v>
+      </c>
+      <c r="F502" t="n">
+        <v>324.77</v>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>329.14</v>
+      </c>
+      <c r="C503" t="n">
+        <v>325.95</v>
+      </c>
+      <c r="D503" t="n">
+        <v>316.74</v>
+      </c>
+      <c r="E503" t="n">
+        <v>317.29</v>
+      </c>
+      <c r="F503" t="n">
+        <v>323.42</v>
+      </c>
+      <c r="G503" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13952,7 +14033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B578"/>
+  <dimension ref="A1:B581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19735,6 +19816,36 @@
       </c>
       <c r="B578" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>0.73</v>
       </c>
     </row>
   </sheetData>
@@ -19903,28 +20014,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09790850536566592</v>
+        <v>0.09784895873995539</v>
       </c>
       <c r="J2" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K2" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04395789583063614</v>
+        <v>0.04446482951990904</v>
       </c>
       <c r="M2" t="n">
-        <v>2.689832811821501</v>
+        <v>2.677796526813441</v>
       </c>
       <c r="N2" t="n">
-        <v>12.30686803278006</v>
+        <v>12.23657761490927</v>
       </c>
       <c r="O2" t="n">
-        <v>3.508114598011311</v>
+        <v>3.498081990878612</v>
       </c>
       <c r="P2" t="n">
-        <v>327.5826724892993</v>
+        <v>327.5832941087581</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19981,28 +20092,28 @@
         <v>0.08260000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09109168501646896</v>
+        <v>0.09417669383570651</v>
       </c>
       <c r="J3" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K3" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02915315456180201</v>
+        <v>0.03142790178313026</v>
       </c>
       <c r="M3" t="n">
-        <v>3.075357009318052</v>
+        <v>3.071712939187649</v>
       </c>
       <c r="N3" t="n">
-        <v>16.31132415611261</v>
+        <v>16.25627187633456</v>
       </c>
       <c r="O3" t="n">
-        <v>4.038728036908726</v>
+        <v>4.031906729617459</v>
       </c>
       <c r="P3" t="n">
-        <v>321.2547341272388</v>
+        <v>321.2228709404672</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20059,28 +20170,28 @@
         <v>0.1285</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09385408909686936</v>
+        <v>0.09773266634224391</v>
       </c>
       <c r="J4" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K4" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04740805169994999</v>
+        <v>0.05154501020833402</v>
       </c>
       <c r="M4" t="n">
-        <v>2.578261525966499</v>
+        <v>2.580907929905667</v>
       </c>
       <c r="N4" t="n">
-        <v>10.44787035778804</v>
+        <v>10.45266657944573</v>
       </c>
       <c r="O4" t="n">
-        <v>3.23231656212507</v>
+        <v>3.23305839406679</v>
       </c>
       <c r="P4" t="n">
-        <v>311.5062757564336</v>
+        <v>311.466217912001</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20137,28 +20248,28 @@
         <v>0.1609</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009758670142917427</v>
+        <v>0.01193023938973147</v>
       </c>
       <c r="J5" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K5" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004881080501841772</v>
+        <v>0.0007378534695139383</v>
       </c>
       <c r="M5" t="n">
-        <v>2.583050816171733</v>
+        <v>2.576017779938359</v>
       </c>
       <c r="N5" t="n">
-        <v>11.51118014817092</v>
+        <v>11.46370853916208</v>
       </c>
       <c r="O5" t="n">
-        <v>3.392813014029938</v>
+        <v>3.385809879358568</v>
       </c>
       <c r="P5" t="n">
-        <v>315.4252539595242</v>
+        <v>315.4028241274346</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20215,28 +20326,28 @@
         <v>0.1333</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0114094502743029</v>
+        <v>0.01466821530208154</v>
       </c>
       <c r="J6" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K6" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004951359620267715</v>
+        <v>0.00082660698187631</v>
       </c>
       <c r="M6" t="n">
-        <v>2.894836797882779</v>
+        <v>2.896371346476578</v>
       </c>
       <c r="N6" t="n">
-        <v>15.51159509386102</v>
+        <v>15.46727654306488</v>
       </c>
       <c r="O6" t="n">
-        <v>3.938476240103655</v>
+        <v>3.932845858035232</v>
       </c>
       <c r="P6" t="n">
-        <v>320.9729452417694</v>
+        <v>320.939288237853</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20274,7 +20385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G500"/>
+  <dimension ref="A1:G503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38777,6 +38888,117 @@
         </is>
       </c>
     </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>-46.38398954377084,168.01547041188593</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>-46.38380412867463,168.01461389159186</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>-46.38358154403326,168.01377304143386</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>-46.38343114191901,168.0129017619718</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>-46.383341710619995,168.01200477769768</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>-46.3839878189656,168.01547113897726</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>-46.383807492035736,168.0146124737344</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>-46.383581888992474,168.01377289600978</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>-46.38343683373021,168.0128993624218</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>-46.3833474024146,168.01200237808897</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>-46.38397531412746,168.01547641038795</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>-46.3838002478733,168.01461552758107</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>-46.38357326501203,168.0137765316106</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>-46.3834304520025,168.01290205282632</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>-46.383335760107386,168.01200728637892</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0536/nzd0536.xlsx
+++ b/data/nzd0536/nzd0536.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G503"/>
+  <dimension ref="A1:G505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14019,6 +14019,60 @@
       <c r="G503" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:26:46+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>328.39</v>
+      </c>
+      <c r="C504" t="n">
+        <v>324.98</v>
+      </c>
+      <c r="D504" t="n">
+        <v>315.97</v>
+      </c>
+      <c r="E504" t="n">
+        <v>316.6</v>
+      </c>
+      <c r="F504" t="n">
+        <v>322.58</v>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>329.32</v>
+      </c>
+      <c r="C505" t="n">
+        <v>325.63</v>
+      </c>
+      <c r="D505" t="n">
+        <v>316.58</v>
+      </c>
+      <c r="E505" t="n">
+        <v>317.29</v>
+      </c>
+      <c r="F505" t="n">
+        <v>323.43</v>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -14033,7 +14087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B581"/>
+  <dimension ref="A1:B583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19846,6 +19900,26 @@
       </c>
       <c r="B581" t="n">
         <v>0.73</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>
@@ -20014,28 +20088,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09784895873995539</v>
+        <v>0.09680002553106989</v>
       </c>
       <c r="J2" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K2" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04446482951990904</v>
+        <v>0.04390100825188614</v>
       </c>
       <c r="M2" t="n">
-        <v>2.677796526813441</v>
+        <v>2.672823893820389</v>
       </c>
       <c r="N2" t="n">
-        <v>12.23657761490927</v>
+        <v>12.19624933941723</v>
       </c>
       <c r="O2" t="n">
-        <v>3.498081990878612</v>
+        <v>3.492312892542309</v>
       </c>
       <c r="P2" t="n">
-        <v>327.5832941087581</v>
+        <v>327.5941515604466</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20092,28 +20166,28 @@
         <v>0.08260000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09417669383570651</v>
+        <v>0.09535122707309046</v>
       </c>
       <c r="J3" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K3" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03142790178313026</v>
+        <v>0.0324503665398056</v>
       </c>
       <c r="M3" t="n">
-        <v>3.071712939187649</v>
+        <v>3.065124445325663</v>
       </c>
       <c r="N3" t="n">
-        <v>16.25627187633456</v>
+        <v>16.20142459649188</v>
       </c>
       <c r="O3" t="n">
-        <v>4.031906729617459</v>
+        <v>4.025099327531171</v>
       </c>
       <c r="P3" t="n">
-        <v>321.2228709404672</v>
+        <v>321.2107102216212</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20170,28 +20244,28 @@
         <v>0.1285</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09773266634224391</v>
+        <v>0.09938907367669829</v>
       </c>
       <c r="J4" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K4" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05154501020833402</v>
+        <v>0.05357115203248253</v>
       </c>
       <c r="M4" t="n">
-        <v>2.580907929905667</v>
+        <v>2.578476798084438</v>
       </c>
       <c r="N4" t="n">
-        <v>10.45266657944573</v>
+        <v>10.42992666000332</v>
       </c>
       <c r="O4" t="n">
-        <v>3.23305839406679</v>
+        <v>3.229539697852207</v>
       </c>
       <c r="P4" t="n">
-        <v>311.466217912001</v>
+        <v>311.4490686319486</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20248,28 +20322,28 @@
         <v>0.1609</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01193023938973147</v>
+        <v>0.01286347080430015</v>
       </c>
       <c r="J5" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K5" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0007378534695139383</v>
+        <v>0.0008648675046876164</v>
       </c>
       <c r="M5" t="n">
-        <v>2.576017779938359</v>
+        <v>2.569434220413638</v>
       </c>
       <c r="N5" t="n">
-        <v>11.46370853916208</v>
+        <v>11.42452009456077</v>
       </c>
       <c r="O5" t="n">
-        <v>3.385809879358568</v>
+        <v>3.380017765420881</v>
       </c>
       <c r="P5" t="n">
-        <v>315.4028241274346</v>
+        <v>315.3931614446949</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20326,28 +20400,28 @@
         <v>0.1333</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01466821530208154</v>
+        <v>0.01594178015695756</v>
       </c>
       <c r="J6" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K6" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00082660698187631</v>
+        <v>0.0009841916246106086</v>
       </c>
       <c r="M6" t="n">
-        <v>2.896371346476578</v>
+        <v>2.892219691637902</v>
       </c>
       <c r="N6" t="n">
-        <v>15.46727654306488</v>
+        <v>15.4174771085755</v>
       </c>
       <c r="O6" t="n">
-        <v>3.932845858035232</v>
+        <v>3.92650953246971</v>
       </c>
       <c r="P6" t="n">
-        <v>320.939288237853</v>
+        <v>320.9261019104763</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20385,7 +20459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G503"/>
+  <dimension ref="A1:G505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38999,6 +39073,80 @@
         </is>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:26:46+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>-46.38396884610759,168.01547913697866</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-46.38379188259035,168.01461905404574</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>-46.38356662454697,168.01377933102236</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>-46.383424501472525,168.01290456144616</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>-46.383328516004966,168.01201034042487</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>-46.38397686645221,168.01547575600608</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>-46.38379748819235,168.01461669095096</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>-46.38357188517515,168.01377711330662</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>-46.3834304520025,168.01290205282632</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>-46.38333584634671,168.0120072500212</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0536/nzd0536.xlsx
+++ b/data/nzd0536/nzd0536.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G505"/>
+  <dimension ref="A1:G506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14073,6 +14073,33 @@
       <c r="G505" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:45+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>327.36</v>
+      </c>
+      <c r="C506" t="n">
+        <v>323.7</v>
+      </c>
+      <c r="D506" t="n">
+        <v>314.58</v>
+      </c>
+      <c r="E506" t="n">
+        <v>315.86</v>
+      </c>
+      <c r="F506" t="n">
+        <v>321.12</v>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -14087,7 +14114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B583"/>
+  <dimension ref="A1:B584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19920,6 +19947,16 @@
       </c>
       <c r="B583" t="n">
         <v>1.12</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -20088,28 +20125,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09680002553106989</v>
+        <v>0.09570223244472001</v>
       </c>
       <c r="J2" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K2" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04390100825188614</v>
+        <v>0.04308252470707985</v>
       </c>
       <c r="M2" t="n">
-        <v>2.672823893820389</v>
+        <v>2.673450531812703</v>
       </c>
       <c r="N2" t="n">
-        <v>12.19624933941723</v>
+        <v>12.18824624676292</v>
       </c>
       <c r="O2" t="n">
-        <v>3.492312892542309</v>
+        <v>3.491166888987538</v>
       </c>
       <c r="P2" t="n">
-        <v>327.5941515604466</v>
+        <v>327.6055662698869</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20166,28 +20203,28 @@
         <v>0.08260000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09535122707309046</v>
+        <v>0.09531115787450541</v>
       </c>
       <c r="J3" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K3" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0324503665398056</v>
+        <v>0.03256420251729852</v>
       </c>
       <c r="M3" t="n">
-        <v>3.065124445325663</v>
+        <v>3.059276280826772</v>
       </c>
       <c r="N3" t="n">
-        <v>16.20142459649188</v>
+        <v>16.16936408035512</v>
       </c>
       <c r="O3" t="n">
-        <v>4.025099327531171</v>
+        <v>4.02111478079837</v>
       </c>
       <c r="P3" t="n">
-        <v>321.2107102216212</v>
+        <v>321.211126855926</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20244,28 +20281,28 @@
         <v>0.1285</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09938907367669829</v>
+        <v>0.0995557278389229</v>
       </c>
       <c r="J4" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K4" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05357115203248253</v>
+        <v>0.05396680209218574</v>
       </c>
       <c r="M4" t="n">
-        <v>2.578476798084438</v>
+        <v>2.574147828264467</v>
       </c>
       <c r="N4" t="n">
-        <v>10.42992666000332</v>
+        <v>10.40964548069066</v>
       </c>
       <c r="O4" t="n">
-        <v>3.229539697852207</v>
+        <v>3.226398221033892</v>
       </c>
       <c r="P4" t="n">
-        <v>311.4490686319486</v>
+        <v>311.4473357836893</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20322,28 +20359,28 @@
         <v>0.1609</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01286347080430015</v>
+        <v>0.01290720847525324</v>
       </c>
       <c r="J5" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K5" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0008648675046876164</v>
+        <v>0.0008746418893418317</v>
       </c>
       <c r="M5" t="n">
-        <v>2.569434220413638</v>
+        <v>2.564516300206906</v>
       </c>
       <c r="N5" t="n">
-        <v>11.42452009456077</v>
+        <v>11.4019229147152</v>
       </c>
       <c r="O5" t="n">
-        <v>3.380017765420881</v>
+        <v>3.376673350313175</v>
       </c>
       <c r="P5" t="n">
-        <v>315.3931614446949</v>
+        <v>315.3927066660925</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20400,28 +20437,28 @@
         <v>0.1333</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01594178015695756</v>
+        <v>0.01585144660094275</v>
       </c>
       <c r="J6" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K6" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009841916246106086</v>
+        <v>0.000977420164002929</v>
       </c>
       <c r="M6" t="n">
-        <v>2.892219691637902</v>
+        <v>2.886904482131305</v>
       </c>
       <c r="N6" t="n">
-        <v>15.4174771085755</v>
+        <v>15.3870567894515</v>
       </c>
       <c r="O6" t="n">
-        <v>3.92650953246971</v>
+        <v>3.92263390969021</v>
       </c>
       <c r="P6" t="n">
-        <v>320.9261019104763</v>
+        <v>320.9270411870189</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20459,7 +20496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G505"/>
+  <dimension ref="A1:G506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39147,6 +39184,43 @@
         </is>
       </c>
     </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:45+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>-46.38395996336014,168.0154828814954</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>-46.383780843866205,168.01462370752313</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>-46.38355463721369,168.01378438450405</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>-46.38341811974464,168.01290725184936</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>-46.38331592506478,168.01201564864547</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
